--- a/Luban/DataTables/Datas/Condition.xlsx
+++ b/Luban/DataTables/Datas/Condition.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26880" windowHeight="9285"/>
+    <workbookView windowWidth="31425" windowHeight="11640"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t>##var</t>
   </si>
@@ -38,13 +38,7 @@
     <t>##模块</t>
   </si>
   <si>
-    <t>Cn</t>
-  </si>
-  <si>
-    <t>En</t>
-  </si>
-  <si>
-    <t>Cn1</t>
+    <t>Flags</t>
   </si>
   <si>
     <t>##type</t>
@@ -65,70 +59,13 @@
     <t>##</t>
   </si>
   <si>
-    <t>中文</t>
-  </si>
-  <si>
-    <t>英文</t>
-  </si>
-  <si>
-    <t>繁中</t>
-  </si>
-  <si>
-    <t>等级</t>
-  </si>
-  <si>
-    <t>经验</t>
-  </si>
-  <si>
-    <t>金币</t>
-  </si>
-  <si>
-    <t>钻石</t>
-  </si>
-  <si>
-    <t>花1</t>
-  </si>
-  <si>
-    <t>花2</t>
-  </si>
-  <si>
-    <t>叶</t>
-  </si>
-  <si>
-    <t>星1</t>
-  </si>
-  <si>
-    <t>星2</t>
-  </si>
-  <si>
-    <t>商店</t>
-  </si>
-  <si>
-    <t>Shop</t>
-  </si>
-  <si>
-    <t>英雄</t>
-  </si>
-  <si>
-    <t>Hero</t>
-  </si>
-  <si>
-    <t>游戏</t>
-  </si>
-  <si>
-    <t>Game</t>
-  </si>
-  <si>
-    <t>事件</t>
-  </si>
-  <si>
-    <t>Event</t>
-  </si>
-  <si>
-    <t>设置</t>
-  </si>
-  <si>
-    <t>Setting</t>
+    <t>flag1</t>
+  </si>
+  <si>
+    <t>flag2</t>
+  </si>
+  <si>
+    <t>条件运算符</t>
   </si>
 </sst>
 </file>
@@ -744,7 +681,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -753,6 +690,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1094,225 +1034,158 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
       <c r="B6" s="2">
-        <v>1001</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
       <c r="B7" s="2">
-        <v>1002</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
       <c r="B8" s="2">
-        <v>1010</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
       <c r="B9" s="2">
-        <v>1011</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
       <c r="B10" s="2">
-        <v>1012</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
       <c r="B11" s="2">
-        <v>1013</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
       <c r="B12" s="2">
-        <v>1014</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
       <c r="B13" s="2">
-        <v>1015</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
       <c r="B14" s="2">
-        <v>1016</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
       <c r="B17" s="2">
         <v>100101</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5">
+    </row>
+    <row r="18" spans="2:2">
       <c r="B18" s="2">
         <v>100102</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5">
+    </row>
+    <row r="19" spans="2:2">
       <c r="B19" s="2">
         <v>100103</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5">
+    </row>
+    <row r="20" spans="2:2">
       <c r="B20" s="2">
         <v>100104</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5">
+    </row>
+    <row r="21" spans="2:2">
       <c r="B21" s="2">
         <v>100105</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>33</v>
-      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D1:F1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
